--- a/artifacts/source_ingestion/ipos_main_ctrl_20260921_143819/comparison_results.xlsx
+++ b/artifacts/source_ingestion/ipos_main_ctrl_20260921_143819/comparison_results.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2445" yWindow="-13530" windowWidth="26355" windowHeight="11100" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="5175" yWindow="-10545" windowWidth="14400" windowHeight="7275" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Ingestion Review" sheetId="1" state="visible" r:id="rId1"/>
@@ -33,7 +33,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -48,11 +48,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE2F0D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -73,7 +68,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -85,9 +80,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -603,7 +595,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M2" s="5" t="inlineStr">
+      <c r="M2" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -667,7 +659,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M3" s="5" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -731,7 +723,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M4" s="5" t="inlineStr">
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -795,7 +787,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M5" s="5" t="inlineStr">
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -859,7 +851,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M6" s="5" t="inlineStr">
+      <c r="M6" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -927,7 +919,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M7" s="5" t="inlineStr">
+      <c r="M7" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -991,7 +983,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M8" s="5" t="inlineStr">
+      <c r="M8" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -1055,7 +1047,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M9" s="5" t="inlineStr">
+      <c r="M9" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -1119,7 +1111,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M10" s="5" t="inlineStr">
+      <c r="M10" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -1183,7 +1175,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M11" s="5" t="inlineStr">
+      <c r="M11" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -1247,7 +1239,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M12" s="5" t="inlineStr">
+      <c r="M12" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -1311,7 +1303,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M13" s="5" t="inlineStr">
+      <c r="M13" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -1375,7 +1367,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M14" s="5" t="inlineStr">
+      <c r="M14" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -1439,7 +1431,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M15" s="5" t="inlineStr">
+      <c r="M15" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -1503,7 +1495,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M16" s="5" t="inlineStr">
+      <c r="M16" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -1567,7 +1559,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M17" s="5" t="inlineStr">
+      <c r="M17" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -1631,7 +1623,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M18" s="5" t="inlineStr">
+      <c r="M18" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -1695,7 +1687,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M19" s="5" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -1759,7 +1751,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M20" s="5" t="inlineStr">
+      <c r="M20" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -1823,7 +1815,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M21" s="5" t="inlineStr">
+      <c r="M21" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -1887,7 +1879,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M22" s="5" t="inlineStr">
+      <c r="M22" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -1951,7 +1943,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M23" s="5" t="inlineStr">
+      <c r="M23" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -2015,7 +2007,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M24" s="5" t="inlineStr">
+      <c r="M24" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -2079,7 +2071,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M25" s="5" t="inlineStr">
+      <c r="M25" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -2143,7 +2135,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M26" s="5" t="inlineStr">
+      <c r="M26" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -2207,7 +2199,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M27" s="5" t="inlineStr">
+      <c r="M27" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -2271,7 +2263,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M28" s="5" t="inlineStr">
+      <c r="M28" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -2335,7 +2327,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M29" s="5" t="inlineStr">
+      <c r="M29" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -2399,7 +2391,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M30" s="5" t="inlineStr">
+      <c r="M30" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -2463,7 +2455,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M31" s="5" t="inlineStr">
+      <c r="M31" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -2527,7 +2519,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M32" s="5" t="inlineStr">
+      <c r="M32" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -2591,7 +2583,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M33" s="5" t="inlineStr">
+      <c r="M33" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -2655,7 +2647,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M34" s="5" t="inlineStr">
+      <c r="M34" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -2719,7 +2711,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M35" s="5" t="inlineStr">
+      <c r="M35" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -2783,7 +2775,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M36" s="5" t="inlineStr">
+      <c r="M36" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -2847,7 +2839,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M37" s="5" t="inlineStr">
+      <c r="M37" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -2911,7 +2903,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M38" s="5" t="inlineStr">
+      <c r="M38" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -2975,7 +2967,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M39" s="5" t="inlineStr">
+      <c r="M39" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -3039,7 +3031,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M40" s="5" t="inlineStr">
+      <c r="M40" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -3103,7 +3095,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M41" s="5" t="inlineStr">
+      <c r="M41" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -3167,7 +3159,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M42" s="5" t="inlineStr">
+      <c r="M42" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -3231,7 +3223,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M43" s="5" t="inlineStr">
+      <c r="M43" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -3295,7 +3287,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M44" s="5" t="inlineStr">
+      <c r="M44" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -3359,7 +3351,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M45" s="5" t="inlineStr">
+      <c r="M45" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -3423,7 +3415,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M46" s="5" t="inlineStr">
+      <c r="M46" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -3487,7 +3479,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M47" s="5" t="inlineStr">
+      <c r="M47" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -3551,7 +3543,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M48" s="5" t="inlineStr">
+      <c r="M48" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -3615,7 +3607,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M49" s="5" t="inlineStr">
+      <c r="M49" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -3679,7 +3671,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M50" s="5" t="inlineStr">
+      <c r="M50" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -3743,7 +3735,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M51" s="5" t="inlineStr">
+      <c r="M51" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -3807,7 +3799,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M52" s="5" t="inlineStr">
+      <c r="M52" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -3871,7 +3863,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M53" s="5" t="inlineStr">
+      <c r="M53" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -3935,7 +3927,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M54" s="5" t="inlineStr">
+      <c r="M54" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -4003,7 +3995,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M55" s="5" t="inlineStr">
+      <c r="M55" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -4067,7 +4059,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M56" s="5" t="inlineStr">
+      <c r="M56" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -4131,7 +4123,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M57" s="5" t="inlineStr">
+      <c r="M57" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -4195,7 +4187,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M58" s="5" t="inlineStr">
+      <c r="M58" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -4259,7 +4251,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M59" s="5" t="inlineStr">
+      <c r="M59" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -4323,7 +4315,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M60" s="5" t="inlineStr">
+      <c r="M60" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -4387,7 +4379,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M61" s="5" t="inlineStr">
+      <c r="M61" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -4451,7 +4443,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M62" s="5" t="inlineStr">
+      <c r="M62" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -4515,7 +4507,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M63" s="5" t="inlineStr">
+      <c r="M63" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -4579,7 +4571,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M64" s="5" t="inlineStr">
+      <c r="M64" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -4643,7 +4635,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M65" s="5" t="inlineStr">
+      <c r="M65" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -4707,7 +4699,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M66" s="5" t="inlineStr">
+      <c r="M66" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -4771,7 +4763,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M67" s="5" t="inlineStr">
+      <c r="M67" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -4835,7 +4827,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M68" s="5" t="inlineStr">
+      <c r="M68" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -4899,7 +4891,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M69" s="5" t="inlineStr">
+      <c r="M69" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -4963,7 +4955,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M70" s="5" t="inlineStr">
+      <c r="M70" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -5027,7 +5019,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M71" s="5" t="inlineStr">
+      <c r="M71" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -5091,7 +5083,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M72" s="5" t="inlineStr">
+      <c r="M72" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -5155,7 +5147,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M73" s="5" t="inlineStr">
+      <c r="M73" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -5219,7 +5211,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M74" s="5" t="inlineStr">
+      <c r="M74" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -5283,7 +5275,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M75" s="5" t="inlineStr">
+      <c r="M75" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -5347,7 +5339,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M76" s="5" t="inlineStr">
+      <c r="M76" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -5411,7 +5403,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M77" s="5" t="inlineStr">
+      <c r="M77" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -5475,7 +5467,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M78" s="5" t="inlineStr">
+      <c r="M78" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -5539,7 +5531,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M79" s="5" t="inlineStr">
+      <c r="M79" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -5603,7 +5595,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M80" s="5" t="inlineStr">
+      <c r="M80" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -5667,7 +5659,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M81" s="5" t="inlineStr">
+      <c r="M81" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -5731,7 +5723,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M82" s="5" t="inlineStr">
+      <c r="M82" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -5795,7 +5787,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M83" s="5" t="inlineStr">
+      <c r="M83" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -5859,7 +5851,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M84" s="5" t="inlineStr">
+      <c r="M84" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -5923,7 +5915,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M85" s="5" t="inlineStr">
+      <c r="M85" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -5987,7 +5979,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M86" s="5" t="inlineStr">
+      <c r="M86" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -6051,7 +6043,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M87" s="5" t="inlineStr">
+      <c r="M87" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -6115,7 +6107,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M88" s="5" t="inlineStr">
+      <c r="M88" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -6179,7 +6171,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M89" s="5" t="inlineStr">
+      <c r="M89" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -6243,7 +6235,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M90" s="5" t="inlineStr">
+      <c r="M90" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -6307,7 +6299,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M91" s="5" t="inlineStr">
+      <c r="M91" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -6371,7 +6363,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M92" s="5" t="inlineStr">
+      <c r="M92" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -6435,7 +6427,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M93" s="5" t="inlineStr">
+      <c r="M93" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -6499,7 +6491,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M94" s="5" t="inlineStr">
+      <c r="M94" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -6563,7 +6555,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M95" s="5" t="inlineStr">
+      <c r="M95" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -6627,7 +6619,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M96" s="5" t="inlineStr">
+      <c r="M96" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -6691,7 +6683,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M97" s="5" t="inlineStr">
+      <c r="M97" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -6755,7 +6747,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M98" s="5" t="inlineStr">
+      <c r="M98" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -6819,7 +6811,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M99" s="5" t="inlineStr">
+      <c r="M99" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -6883,7 +6875,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M100" s="5" t="inlineStr">
+      <c r="M100" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -6947,7 +6939,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M101" s="5" t="inlineStr">
+      <c r="M101" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -7011,7 +7003,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M102" s="5" t="inlineStr">
+      <c r="M102" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -7075,7 +7067,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M103" s="5" t="inlineStr">
+      <c r="M103" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -7139,7 +7131,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M104" s="5" t="inlineStr">
+      <c r="M104" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -7203,7 +7195,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M105" s="5" t="inlineStr">
+      <c r="M105" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -7267,7 +7259,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M106" s="5" t="inlineStr">
+      <c r="M106" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -7331,7 +7323,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M107" s="5" t="inlineStr">
+      <c r="M107" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -7395,7 +7387,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M108" s="5" t="inlineStr">
+      <c r="M108" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -7459,7 +7451,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M109" s="5" t="inlineStr">
+      <c r="M109" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -7523,7 +7515,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M110" s="5" t="inlineStr">
+      <c r="M110" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -7587,7 +7579,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M111" s="5" t="inlineStr">
+      <c r="M111" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -7651,7 +7643,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M112" s="5" t="inlineStr">
+      <c r="M112" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -7715,7 +7707,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M113" s="5" t="inlineStr">
+      <c r="M113" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -7779,7 +7771,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M114" s="5" t="inlineStr">
+      <c r="M114" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -7843,7 +7835,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M115" s="5" t="inlineStr">
+      <c r="M115" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -7907,7 +7899,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M116" s="5" t="inlineStr">
+      <c r="M116" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -7971,7 +7963,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M117" s="5" t="inlineStr">
+      <c r="M117" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -8035,7 +8027,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M118" s="5" t="inlineStr">
+      <c r="M118" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -8099,7 +8091,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M119" s="5" t="inlineStr">
+      <c r="M119" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -8163,7 +8155,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M120" s="5" t="inlineStr">
+      <c r="M120" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -8227,7 +8219,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M121" s="5" t="inlineStr">
+      <c r="M121" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -8291,7 +8283,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M122" s="5" t="inlineStr">
+      <c r="M122" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -8355,7 +8347,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M123" s="5" t="inlineStr">
+      <c r="M123" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -8419,7 +8411,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M124" s="5" t="inlineStr">
+      <c r="M124" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -8483,7 +8475,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M125" s="5" t="inlineStr">
+      <c r="M125" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -8547,7 +8539,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M126" s="5" t="inlineStr">
+      <c r="M126" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -8611,7 +8603,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M127" s="5" t="inlineStr">
+      <c r="M127" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -8675,7 +8667,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M128" s="5" t="inlineStr">
+      <c r="M128" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -8739,7 +8731,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M129" s="5" t="inlineStr">
+      <c r="M129" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -8803,7 +8795,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M130" s="5" t="inlineStr">
+      <c r="M130" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -8867,7 +8859,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M131" s="5" t="inlineStr">
+      <c r="M131" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -8931,7 +8923,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M132" s="5" t="inlineStr">
+      <c r="M132" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -8995,7 +8987,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M133" s="5" t="inlineStr">
+      <c r="M133" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -9059,7 +9051,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M134" s="5" t="inlineStr">
+      <c r="M134" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -9123,7 +9115,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M135" s="5" t="inlineStr">
+      <c r="M135" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -9187,7 +9179,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M136" s="5" t="inlineStr">
+      <c r="M136" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -9251,7 +9243,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M137" s="5" t="inlineStr">
+      <c r="M137" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -9315,7 +9307,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M138" s="5" t="inlineStr">
+      <c r="M138" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -9379,7 +9371,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M139" s="5" t="inlineStr">
+      <c r="M139" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -9443,7 +9435,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M140" s="5" t="inlineStr">
+      <c r="M140" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -9507,7 +9499,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M141" s="5" t="inlineStr">
+      <c r="M141" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -9571,7 +9563,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M142" s="5" t="inlineStr">
+      <c r="M142" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -9635,7 +9627,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M143" s="5" t="inlineStr">
+      <c r="M143" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -9699,7 +9691,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M144" s="5" t="inlineStr">
+      <c r="M144" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -9763,7 +9755,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M145" s="5" t="inlineStr">
+      <c r="M145" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -9827,7 +9819,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M146" s="5" t="inlineStr">
+      <c r="M146" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -9891,7 +9883,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M147" s="5" t="inlineStr">
+      <c r="M147" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -9955,7 +9947,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M148" s="5" t="inlineStr">
+      <c r="M148" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -10019,7 +10011,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M149" s="5" t="inlineStr">
+      <c r="M149" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -10083,7 +10075,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M150" s="5" t="inlineStr">
+      <c r="M150" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -10147,7 +10139,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M151" s="5" t="inlineStr">
+      <c r="M151" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -10211,7 +10203,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M152" s="5" t="inlineStr">
+      <c r="M152" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -10275,7 +10267,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M153" s="5" t="inlineStr">
+      <c r="M153" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -10339,7 +10331,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M154" s="5" t="inlineStr">
+      <c r="M154" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -10403,7 +10395,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M155" s="5" t="inlineStr">
+      <c r="M155" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -10467,7 +10459,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M156" s="5" t="inlineStr">
+      <c r="M156" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -10531,7 +10523,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M157" s="5" t="inlineStr">
+      <c r="M157" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -10595,7 +10587,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M158" s="5" t="inlineStr">
+      <c r="M158" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -10659,7 +10651,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M159" s="5" t="inlineStr">
+      <c r="M159" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -10723,7 +10715,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M160" s="5" t="inlineStr">
+      <c r="M160" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -10787,7 +10779,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M161" s="5" t="inlineStr">
+      <c r="M161" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -10851,7 +10843,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M162" s="5" t="inlineStr">
+      <c r="M162" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -10915,7 +10907,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M163" s="5" t="inlineStr">
+      <c r="M163" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -10979,7 +10971,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M164" s="5" t="inlineStr">
+      <c r="M164" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -11043,7 +11035,7 @@
           <t>manual_review</t>
         </is>
       </c>
-      <c r="M165" s="5" t="inlineStr">
+      <c r="M165" s="4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
